--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,256 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135263276</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106285</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>340</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hellidenskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>439771</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6447283</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett huvudsakligen överblommat bestånd på ca 20 kvadratmeter på sydöstra sidan av en skogsväg intill en välvuxen tall i Hellidenskogen på angiven latitud/longitud ca 1,2 km SSSV om Hellidens folkhögskola. Några få ännu blommande exemplar men i princip var beståndet i slutet av blomningen. Minst tusen blommande skott kunde uppskattas på platsen idag.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Uno Unger</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135263280</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hellidenskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>439771</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6447283</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inga blommande skott noterades men en hel del sterila revor sågs längs en sträcka på ca 250 m från där vi parkerade bilarna och fram till rylbeståndet.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Uno Unger</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+          <t>Christina Hansen, Olof Jansson, Peter Laudon, Eva Andersson, Erik Ljungstrand, Uno Unger</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+          <t>Christina Hansen, Olof Jansson, Peter Laudon, Eva Andersson, Erik Ljungstrand, Uno Unger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120844760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,10 +931,15 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christina Hansen, Olof Jansson, Peter Laudon, Eva Andersson, Erik Ljungstrand, Uno Unger</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135263276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,12 +1057,22 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Hansen, Olof Jansson, Peter Laudon, Eva Andersson, Erik Ljungstrand, Uno Unger</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135263280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135263276</v>
       </c>
       <c r="B3" t="n">
-        <v>106285</v>
+        <v>106340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>135263280</v>
       </c>
       <c r="B4" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135263276</v>
       </c>
       <c r="B3" t="n">
-        <v>106340</v>
+        <v>106367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>135263280</v>
       </c>
       <c r="B4" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -931,7 +931,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+          <t>Christina Hansen, Olof Jansson, Peter Laudon, Eva Andersson, Erik Ljungstrand, Uno Unger</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+          <t>Christina Hansen, Olof Jansson, Peter Laudon, Eva Andersson, Erik Ljungstrand, Uno Unger</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,9 +807,271 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135263276</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106372</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>340</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hellidenskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>439771</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6447283</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett huvudsakligen överblommat bestånd på ca 20 kvadratmeter på sydöstra sidan av en skogsväg intill en välvuxen tall i Hellidenskogen på angiven latitud/longitud ca 1,2 km SSSV om Hellidens folkhögskola. Några få ännu blommande exemplar men i princip var beståndet i slutet av blomningen. Minst tusen blommande skott kunde uppskattas på platsen idag.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Uno Unger</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135263276</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135263280</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hellidenskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>439771</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6447283</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tidaholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Agnetorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inga blommande skott noterades men en hel del sterila revor sågs längs en sträcka på ca 250 m från där vi parkerade bilarna och fram till rylbeståndet.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Uno Unger</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Peter Laudon, Olof Jansson, Christina Hansen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135263280</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 965-2022 artfynd.xlsx
+++ b/artfynd/S 965-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135263276</v>
       </c>
       <c r="B3" t="n">
-        <v>106372</v>
+        <v>106374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>135263280</v>
       </c>
       <c r="B4" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
